--- a/artfynd/A 25653-2019 artfynd.xlsx
+++ b/artfynd/A 25653-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25653-2019 artfynd.xlsx
+++ b/artfynd/A 25653-2019 artfynd.xlsx
@@ -960,7 +960,7 @@
         <v>71933941</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
+        <v>96885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729800.8970129495</v>
+        <v>729801</v>
       </c>
       <c r="R4" t="n">
-        <v>7242218.105792033</v>
+        <v>7242218</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,22 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2001-01-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2002-01-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,7 +1062,7 @@
         <v>71933940</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
+        <v>96885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729817.1748226304</v>
+        <v>729817</v>
       </c>
       <c r="R5" t="n">
-        <v>7242133.884410279</v>
+        <v>7242134</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,22 +1129,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2001-01-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2002-01-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
